--- a/Packages/cn.etetet.yiuilubangen/Assets/Editor/Luban/Base/__tables__.xlsx
+++ b/Packages/cn.etetet.yiuilubangen/Assets/Editor/Luban/Base/__tables__.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="30720" windowHeight="14055"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="30">
   <si>
     <t>##var</t>
   </si>
@@ -114,6 +114,9 @@
   </si>
   <si>
     <t>Unit</t>
+  </si>
+  <si>
+    <t>Audio</t>
   </si>
 </sst>
 </file>
@@ -1055,8 +1058,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="4"/>
+  <dimension ref="A1:L6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5"/>
   <cols>
     <col min="2" max="2" width="12.375" customWidth="1"/>
     <col min="3" max="3" width="34.25" customWidth="1"/>
@@ -1156,52 +1159,76 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" customFormat="1" spans="2:12">
+    <row r="4" customFormat="1" spans="1:12">
       <c r="B4" t="s">
         <v>27</v>
       </c>
       <c r="C4" t="str">
-        <f>_xlfn.CONCAT(B4,"ConfigCategory")</f>
+        <f t="shared" ref="C4:C6" si="0">_xlfn.CONCAT(B4,"ConfigCategory")</f>
         <v>AIConfigCategory</v>
       </c>
       <c r="D4" t="str">
-        <f>_xlfn.CONCAT(B4,"Config")</f>
+        <f t="shared" ref="D4:D6" si="1">_xlfn.CONCAT(B4,"Config")</f>
         <v>AIConfig</v>
       </c>
       <c r="E4" t="b">
         <v>1</v>
       </c>
       <c r="F4" t="str">
-        <f>_xlfn.CONCAT(B4,".xlsx")</f>
+        <f t="shared" ref="F4:F6" si="2">_xlfn.CONCAT(B4,".xlsx")</f>
         <v>AI.xlsx</v>
       </c>
       <c r="L4" t="str">
-        <f>_xlfn.CONCAT(B4,"ConfigCategory")</f>
+        <f t="shared" ref="L4:L6" si="3">_xlfn.CONCAT(B4,"ConfigCategory")</f>
         <v>AIConfigCategory</v>
       </c>
     </row>
-    <row r="5" customFormat="1" spans="2:12">
+    <row r="5" customFormat="1" spans="1:12">
       <c r="B5" t="s">
         <v>28</v>
       </c>
       <c r="C5" t="str">
-        <f>_xlfn.CONCAT(B5,"ConfigCategory")</f>
+        <f t="shared" si="0"/>
         <v>UnitConfigCategory</v>
       </c>
       <c r="D5" t="str">
-        <f>_xlfn.CONCAT(B5,"Config")</f>
+        <f t="shared" si="1"/>
         <v>UnitConfig</v>
       </c>
       <c r="E5" t="b">
         <v>1</v>
       </c>
       <c r="F5" t="str">
-        <f>_xlfn.CONCAT(B5,".xlsx")</f>
+        <f t="shared" si="2"/>
         <v>Unit.xlsx</v>
       </c>
       <c r="L5" t="str">
-        <f>_xlfn.CONCAT(B5,"ConfigCategory")</f>
+        <f t="shared" si="3"/>
         <v>UnitConfigCategory</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="B6" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" t="str">
+        <f t="shared" si="0"/>
+        <v>AudioConfigCategory</v>
+      </c>
+      <c r="D6" t="str">
+        <f t="shared" si="1"/>
+        <v>AudioConfig</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" t="str">
+        <f>_xlfn.CONCAT(B6,".xlsx")</f>
+        <v>Audio.xlsx</v>
+      </c>
+      <c r="L6" t="str">
+        <f t="shared" si="3"/>
+        <v>AudioConfigCategory</v>
       </c>
     </row>
   </sheetData>
